--- a/assets/chulgo-export-template.xlsx
+++ b/assets/chulgo-export-template.xlsx
@@ -28883,22 +28883,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>박준엽</author>
-  </authors>
-  <commentList>
-    <comment ref="B148" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">박준엽:
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -44640,6 +44624,5 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="51" verticalDpi="4294967293"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/assets/chulgo-export-template.xlsx
+++ b/assets/chulgo-export-template.xlsx
@@ -456,7 +456,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -854,6 +854,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -29457,7 +29466,7 @@
       <c r="D12" s="24" t="n"/>
       <c r="E12" s="24" t="n"/>
       <c r="F12" s="23" t="n"/>
-      <c r="G12" s="102" t="n"/>
+      <c r="G12" s="131" t="n"/>
       <c r="H12" s="99" t="n"/>
       <c r="I12" s="100" t="n"/>
       <c r="J12" s="28" t="n"/>
@@ -29475,7 +29484,7 @@
       <c r="D13" s="24" t="n"/>
       <c r="E13" s="23" t="n"/>
       <c r="F13" s="23" t="n"/>
-      <c r="G13" s="102" t="n"/>
+      <c r="G13" s="131" t="n"/>
       <c r="H13" s="99" t="n"/>
       <c r="I13" s="100" t="n"/>
       <c r="J13" s="28" t="n"/>
@@ -31792,8 +31801,8 @@
       <c r="O147" s="65" t="n"/>
     </row>
     <row r="148" ht="15.95" customHeight="1" s="87">
-      <c r="A148" s="125" t="n"/>
-      <c r="B148" s="126" t="n"/>
+      <c r="A148" s="132" t="n"/>
+      <c r="B148" s="133" t="n"/>
       <c r="C148" s="89" t="n"/>
       <c r="D148" s="89" t="n"/>
       <c r="E148" s="89" t="n"/>
